--- a/光伏配储项目/电价数据/2026/沥沙站.xlsx
+++ b/光伏配储项目/电价数据/2026/沥沙站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5088199999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7475599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57337</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11648</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09472</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08774999999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11335</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03129</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07295</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.08798</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.08395999999999999</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08990000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.00619</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.02712</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.13806</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21095</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.20578</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18403</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21236</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01464</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.17953</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.10867</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.21789</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.25284</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.21572</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18085</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51846</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.49008</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.7826900000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59601</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57086</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60514</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79484</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6402599999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6085700000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7367100000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.88218</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66383</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6735399999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.51576</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.47928</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6285700000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42581</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68953</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.26877</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69598</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.89899</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.73695</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51825</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48828</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46948</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.58066</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.5993099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50868</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.13972</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.46909</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.73511</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.94526</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.63349</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12642</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.26259</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47931</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26573</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.20533</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.6271599999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5211699999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6762400000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.68972</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.72273</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.48292</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75697</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.65038</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5101100000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50325</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.26573</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47392</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43907</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.10652</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16575</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.14169</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19455</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47503</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52942</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48465</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28218</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51749</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6008600000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.55192</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6241100000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47424</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34218</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13784</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05461</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06238</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07135</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.16465</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.18094</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.56908</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13978</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.43639</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5173099999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2982</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26163</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02653</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.02704</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.02372</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04465</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.05305</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.05281</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02925</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04636</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.03927000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.03705</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03239</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03403</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03606</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03538</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03092</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03825</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.03438</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03782</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03977</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.03501</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04019</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05829</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00627</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.13176</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.08292000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35131</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.64374</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04694</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04388</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04005</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.11061</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.02884</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04517</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04413</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03552</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.03759000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04735</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04782</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14282</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33573</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17245</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17103</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15952</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15868</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21409</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45514</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15657</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91487</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86498</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29734</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88955</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63195</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1891</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86976</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5462100000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33291</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03433</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79274</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5317499999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77474</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7789400000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87699</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87478</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4948</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40201</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20911</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8788899999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55106</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62395</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53884</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45608</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59645</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60324</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.68732</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58127</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45193</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8834500000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6361100000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81369</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8617899999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.24571</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35374</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92375</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50196</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16428</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19908</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19779</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42329</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59984</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89115</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35521</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16564</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79538</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66622</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50437</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43065</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42501</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.51654</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24923</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.00479</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.25563</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25691</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42515</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32463</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.25719</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27249</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.20745</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13246</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.14118</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13745</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.12533</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.12415</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22665</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.12496</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.23511</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12282</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09781999999999999</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.08957</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.12301</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.12725</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25542</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45166</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39258</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34936</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5426799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47117</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24754</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24154</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36096</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25145</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.23823</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07241</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25926</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69335</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23154</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28963</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34996</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65395</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78326</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45301</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46015</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34443</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14687</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19949</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.66959</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61627</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.63588</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5156499999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8231900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49925</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.84651</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48643</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36061</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52815</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48066</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45146</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56632</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45418</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52683</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6300399999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17464</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52563</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5205599999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.57189</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7171900000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73402</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.18387</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.81357</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81191</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58488</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83133</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76354</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6230399999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66943</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47889</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46968</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55361</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44316</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45646</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43306</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10915</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18258</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36756</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22933</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22893</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14281</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24871</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16742</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18463</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25633</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21532</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03963000000000001</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01575</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04156</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04840999999999999</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.0245</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03008</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00143</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03758</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01734</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03596</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20691</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26666</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.47151</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3532</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.91272</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.8503500000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.54632</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9331799999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.98846</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.88679</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.90751</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.18888</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27574</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16164</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.14396</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06464</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32401</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49833</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.51947</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.46403</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14026</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32958</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.48145</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49278</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47455</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47917</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47272</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.53665</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36835</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47862</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57129</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5626599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.42609</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.54142</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.60607</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49479</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.52437</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.68362</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.6476000000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37277</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14048</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.24847</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05817</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13601</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20262</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15799</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007019999999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25782</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14949</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05678</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04308</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06542000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17428</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07148</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.20976</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15526</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.18682</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44379</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38429</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.02729</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5527799999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.50266</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.13514</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00835</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02341</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.01486</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.00335</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00461</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.14805</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02778</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17594</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3704</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.50654</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17517</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19669</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.09845999999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.16603</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04589</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.03369</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.03909000000000001</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.09468</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.07084</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.11608</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22479</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15343</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14185</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14431</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.24406</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47816</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39283</v>
       </c>
     </row>
   </sheetData>
